--- a/py文件操作/03_Excel/蜀国考试成绩表.xlsx
+++ b/py文件操作/03_Excel/蜀国考试成绩表.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="期末成绩" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="期末成绩" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C2" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D2" t="n">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="E2" s="2">
         <f>average(B2:D2)</f>
@@ -504,13 +504,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C3" t="n">
         <v>73</v>
       </c>
       <c r="D3" t="n">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="E3" s="2">
         <f>average(B3:D3)</f>
@@ -524,13 +524,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="C4" t="n">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="D4" t="n">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="E4" s="2">
         <f>average(B4:D4)</f>
@@ -544,13 +544,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="C5" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D5" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E5" s="2">
         <f>average(B5:D5)</f>
@@ -567,10 +567,10 @@
         <v>73</v>
       </c>
       <c r="C6" t="n">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="D6" t="n">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="E6" s="2">
         <f>average(B6:D6)</f>

--- a/py文件操作/03_Excel/蜀国考试成绩表.xlsx
+++ b/py文件操作/03_Excel/蜀国考试成绩表.xlsx
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C2" t="n">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="D2" t="n">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="E2" s="2">
         <f>average(B2:D2)</f>
@@ -504,13 +504,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="C3" t="n">
+        <v>70</v>
+      </c>
+      <c r="D3" t="n">
         <v>73</v>
-      </c>
-      <c r="D3" t="n">
-        <v>81</v>
       </c>
       <c r="E3" s="2">
         <f>average(B3:D3)</f>
@@ -524,13 +524,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="C4" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D4" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E4" s="2">
         <f>average(B4:D4)</f>
@@ -544,13 +544,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C5" t="n">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D5" t="n">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="E5" s="2">
         <f>average(B5:D5)</f>
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="C6" t="n">
-        <v>99</v>
+        <v>60</v>
       </c>
       <c r="D6" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E6" s="2">
         <f>average(B6:D6)</f>
